--- a/data/trans_camb/IP16A02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 39,56</t>
+          <t>4,49; 39,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 25,9</t>
+          <t>-11,87; 24,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 48,11</t>
+          <t>3,83; 47,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 17,31</t>
+          <t>-19,71; 17,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 19,94</t>
+          <t>-21,41; 18,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 23,86</t>
+          <t>-18,69; 23,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 22,27</t>
+          <t>-2,81; 22,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 15,0</t>
+          <t>-11,35; 15,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 30,58</t>
+          <t>-0,58; 30,7</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 244,14</t>
+          <t>11,59; 231,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 155,07</t>
+          <t>-33,47; 148,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,7; 275,04</t>
+          <t>10,37; 264,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 60,16</t>
+          <t>-39,53; 60,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,22; 66,08</t>
+          <t>-43,49; 61,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 81,37</t>
+          <t>-36,87; 78,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 85,37</t>
+          <t>-6,59; 85,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 58,43</t>
+          <t>-28,41; 53,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 111,52</t>
+          <t>-2,95; 114,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 12,52</t>
+          <t>-18,02; 13,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 25,11</t>
+          <t>-8,37; 24,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 29,36</t>
+          <t>-3,75; 31,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 6,28</t>
+          <t>-22,93; 6,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 2,77</t>
+          <t>-27,11; 3,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 18,16</t>
+          <t>-14,6; 18,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 4,97</t>
+          <t>-17,77; 4,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 9,67</t>
+          <t>-13,72; 8,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 20,85</t>
+          <t>-5,7; 19,25</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,1; 54,5</t>
+          <t>-43,52; 53,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 104,11</t>
+          <t>-20,05; 99,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 122,66</t>
+          <t>-9,09; 139,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,02; 15,93</t>
+          <t>-43,0; 18,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,12; 7,79</t>
+          <t>-50,19; 13,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 50,4</t>
+          <t>-26,42; 53,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 15,08</t>
+          <t>-37,4; 13,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,55; 28,15</t>
+          <t>-29,55; 24,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 61,58</t>
+          <t>-13,05; 55,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 33,26</t>
+          <t>-6,58; 33,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 17,91</t>
+          <t>-20,54; 18,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 50,4</t>
+          <t>7,76; 49,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 27,76</t>
+          <t>-14,27; 26,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 22,96</t>
+          <t>-18,44; 21,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 26,68</t>
+          <t>-11,64; 27,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 24,73</t>
+          <t>-4,72; 24,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 14,9</t>
+          <t>-13,42; 14,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 32,88</t>
+          <t>3,18; 32,92</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 195,52</t>
+          <t>-18,24; 174,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 105,52</t>
+          <t>-49,35; 112,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,75; 323,54</t>
+          <t>16,78; 282,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 117,39</t>
+          <t>-31,54; 108,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 101,75</t>
+          <t>-38,34; 89,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 111,12</t>
+          <t>-24,97; 123,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 107,18</t>
+          <t>-10,84; 108,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 60,99</t>
+          <t>-31,64; 59,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 140,91</t>
+          <t>7,01; 141,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 28,44</t>
+          <t>-12,31; 27,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 32,38</t>
+          <t>-8,78; 32,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-39,17; 4,57</t>
+          <t>-47,63; 2,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 20,44</t>
+          <t>-16,46; 20,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 13,95</t>
+          <t>-24,39; 12,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 19,76</t>
+          <t>-14,63; 21,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 19,05</t>
+          <t>-9,07; 18,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 18,09</t>
+          <t>-9,18; 18,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 6,29</t>
+          <t>-26,42; 7,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 103,4</t>
+          <t>-25,11; 99,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 115,64</t>
+          <t>-17,05; 116,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,38; 11,09</t>
+          <t>-86,37; 5,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 70,46</t>
+          <t>-35,05; 70,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,3; 50,44</t>
+          <t>-53,41; 42,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 67,45</t>
+          <t>-30,62; 73,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 57,11</t>
+          <t>-19,71; 55,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 54,83</t>
+          <t>-20,21; 56,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 17,48</t>
+          <t>-56,37; 19,98</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 17,1</t>
+          <t>0,06; 17,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 14,89</t>
+          <t>-3,73; 15,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 18,9</t>
+          <t>-10,11; 20,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 6,09</t>
+          <t>-11,77; 6,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 4,46</t>
+          <t>-14,47; 4,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 11,28</t>
+          <t>-6,63; 12,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 8,71</t>
+          <t>-2,91; 9,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 7,25</t>
+          <t>-6,22; 6,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 12,08</t>
+          <t>-5,59; 11,91</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 61,31</t>
+          <t>0,13; 65,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 55,65</t>
+          <t>-10,11; 53,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 61,75</t>
+          <t>-27,65; 68,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 16,34</t>
+          <t>-25,37; 19,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 12,07</t>
+          <t>-30,94; 12,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 30,75</t>
+          <t>-14,43; 33,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 25,23</t>
+          <t>-7,25; 29,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 20,67</t>
+          <t>-15,27; 19,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 34,82</t>
+          <t>-13,95; 34,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 39,15</t>
+          <t>4,86; 39,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 24,44</t>
+          <t>-12,77; 24,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 47,49</t>
+          <t>4,23; 48,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 17,37</t>
+          <t>-18,47; 17,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 18,57</t>
+          <t>-20,54; 19,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 23,55</t>
+          <t>-17,49; 24,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 22,83</t>
+          <t>-3,17; 22,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 15,34</t>
+          <t>-13,61; 14,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 30,7</t>
+          <t>-1,57; 28,23</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,59; 231,72</t>
+          <t>11,06; 233,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,47; 148,06</t>
+          <t>-41,39; 130,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,37; 264,36</t>
+          <t>12,99; 266,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,53; 60,78</t>
+          <t>-37,54; 61,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,49; 61,78</t>
+          <t>-39,84; 75,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 78,33</t>
+          <t>-35,59; 88,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 85,33</t>
+          <t>-7,88; 85,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 53,43</t>
+          <t>-32,95; 57,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 114,64</t>
+          <t>-5,08; 104,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 13,03</t>
+          <t>-18,78; 12,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 24,19</t>
+          <t>-8,69; 24,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 31,49</t>
+          <t>-5,29; 28,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 6,88</t>
+          <t>-23,99; 5,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 3,9</t>
+          <t>-27,2; 3,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 18,76</t>
+          <t>-15,34; 18,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 4,3</t>
+          <t>-15,8; 4,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 8,72</t>
+          <t>-12,39; 9,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 19,25</t>
+          <t>-6,43; 19,26</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,52; 53,53</t>
+          <t>-44,47; 51,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 99,73</t>
+          <t>-20,83; 98,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 139,69</t>
+          <t>-11,49; 113,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 18,1</t>
+          <t>-44,88; 15,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,19; 13,03</t>
+          <t>-50,89; 10,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 53,64</t>
+          <t>-28,88; 48,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 13,09</t>
+          <t>-33,76; 13,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 24,61</t>
+          <t>-26,91; 26,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 55,87</t>
+          <t>-14,18; 56,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 33,16</t>
+          <t>-7,6; 32,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 18,13</t>
+          <t>-19,94; 18,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,76; 49,15</t>
+          <t>7,97; 50,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 26,05</t>
+          <t>-17,05; 26,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 21,15</t>
+          <t>-17,26; 21,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 27,32</t>
+          <t>-12,97; 26,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 24,82</t>
+          <t>-5,05; 25,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 14,6</t>
+          <t>-13,14; 15,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 32,92</t>
+          <t>2,95; 33,1</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 174,44</t>
+          <t>-16,98; 203,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-49,35; 112,55</t>
+          <t>-48,83; 112,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,78; 282,72</t>
+          <t>17,2; 298,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,54; 108,8</t>
+          <t>-37,05; 109,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 89,83</t>
+          <t>-35,69; 87,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 123,24</t>
+          <t>-28,55; 113,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 108,05</t>
+          <t>-13,13; 107,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 59,32</t>
+          <t>-31,59; 71,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,01; 141,22</t>
+          <t>6,23; 143,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 27,9</t>
+          <t>-9,38; 29,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 32,52</t>
+          <t>-8,63; 29,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 2,14</t>
+          <t>-44,56; 4,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 20,91</t>
+          <t>-17,86; 19,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 12,79</t>
+          <t>-24,39; 14,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 21,65</t>
+          <t>-14,51; 20,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 18,03</t>
+          <t>-8,38; 18,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 18,74</t>
+          <t>-10,21; 18,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 7,1</t>
+          <t>-27,93; 6,89</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 99,0</t>
+          <t>-20,82; 102,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 116,6</t>
+          <t>-16,64; 106,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,37; 5,04</t>
+          <t>-80,98; 11,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 70,82</t>
+          <t>-38,32; 60,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,41; 42,81</t>
+          <t>-52,19; 48,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 73,3</t>
+          <t>-30,67; 67,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 55,57</t>
+          <t>-19,52; 58,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 56,65</t>
+          <t>-22,45; 57,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 19,98</t>
+          <t>-59,21; 18,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 17,94</t>
+          <t>-0,03; 17,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 15,16</t>
+          <t>-3,18; 14,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 20,0</t>
+          <t>-11,52; 18,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 6,82</t>
+          <t>-10,18; 8,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 4,24</t>
+          <t>-14,51; 4,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 12,18</t>
+          <t>-8,29; 11,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 9,81</t>
+          <t>-3,6; 9,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 6,66</t>
+          <t>-5,94; 6,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 11,91</t>
+          <t>-5,9; 12,2</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,13; 65,25</t>
+          <t>-0,2; 63,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 53,88</t>
+          <t>-8,35; 50,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 68,1</t>
+          <t>-29,72; 63,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 19,21</t>
+          <t>-22,33; 22,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 12,8</t>
+          <t>-31,73; 11,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 33,96</t>
+          <t>-18,43; 32,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 29,15</t>
+          <t>-8,95; 27,49</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 19,2</t>
+          <t>-14,66; 20,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 34,71</t>
+          <t>-13,6; 35,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,61</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>22,84</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,74</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26,59</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>27,25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,66</t>
+          <t>14,27</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 39,88</t>
+          <t>-19,79; 17,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 24,69</t>
+          <t>-24,67; 19,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 48,4</t>
+          <t>-17,27; 24,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 17,31</t>
+          <t>4,29; 39,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 19,99</t>
+          <t>-11,83; 25,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 24,24</t>
+          <t>4,5; 48,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 22,86</t>
+          <t>-3,12; 22,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 14,91</t>
+          <t>-12,48; 15,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 28,23</t>
+          <t>-2,19; 31,09</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-4,28%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-2,86%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>83,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>17,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,28%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-2,86%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,06; 233,11</t>
+          <t>-40,45; 60,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,39; 130,8</t>
+          <t>-47,22; 66,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,99; 266,67</t>
+          <t>-35,71; 82,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 61,06</t>
+          <t>10,13; 244,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,84; 75,18</t>
+          <t>-35,23; 155,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 88,36</t>
+          <t>14,48; 284,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 85,99</t>
+          <t>-7,22; 85,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,95; 57,39</t>
+          <t>-30,57; 58,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 104,79</t>
+          <t>-5,55; 114,12</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-8,46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-11,37</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,46</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>9,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13,5</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-8,46</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-11,37</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>14,43</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>7,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 12,31</t>
+          <t>-22,7; 6,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 24,58</t>
+          <t>-27,05; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 28,78</t>
+          <t>-13,85; 19,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 5,54</t>
+          <t>-19,14; 12,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 3,49</t>
+          <t>-6,91; 25,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 18,18</t>
+          <t>-3,87; 29,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 4,77</t>
+          <t>-15,34; 4,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 9,38</t>
+          <t>-12,24; 9,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 19,26</t>
+          <t>-4,1; 21,21</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-18,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-24,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-7,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>27,22%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40,83%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-18,38%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-24,7%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,47; 51,05</t>
+          <t>-42,02; 15,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 98,72</t>
+          <t>-51,12; 7,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 113,19</t>
+          <t>-25,96; 52,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 15,0</t>
+          <t>-44,1; 54,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 10,15</t>
+          <t>-16,5; 104,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 48,19</t>
+          <t>-6,52; 129,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 13,9</t>
+          <t>-33,99; 15,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 26,98</t>
+          <t>-27,55; 28,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 56,3</t>
+          <t>-9,09; 65,17</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,95</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>14,59</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,73</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>31,57</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,88</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>32,45</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>19,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 32,8</t>
+          <t>-15,18; 27,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 18,11</t>
+          <t>-17,16; 22,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 50,28</t>
+          <t>-15,01; 26,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 26,02</t>
+          <t>-7,76; 33,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 21,09</t>
+          <t>-20,62; 17,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 26,65</t>
+          <t>10,33; 51,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 25,3</t>
+          <t>-3,92; 24,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 15,93</t>
+          <t>-14,03; 14,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 33,1</t>
+          <t>2,76; 33,5</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16,52%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>48,99%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-2,45%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>105,99%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>108,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>59,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 203,34</t>
+          <t>-31,79; 117,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 112,99</t>
+          <t>-36,59; 101,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,2; 298,13</t>
+          <t>-30,82; 109,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,05; 109,39</t>
+          <t>-17,07; 195,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,69; 87,68</t>
+          <t>-48,37; 105,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 113,12</t>
+          <t>23,45; 335,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 107,27</t>
+          <t>-9,47; 107,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 71,55</t>
+          <t>-32,11; 60,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,23; 143,11</t>
+          <t>7,45; 141,76</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,75</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,57</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>10,79</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-16,84</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,75</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-7,72</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 29,74</t>
+          <t>-16,83; 20,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 29,56</t>
+          <t>-23,52; 13,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 4,64</t>
+          <t>-15,07; 20,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 19,13</t>
+          <t>-11,42; 28,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 14,5</t>
+          <t>-8,46; 32,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 20,42</t>
+          <t>-21,75; 15,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 18,31</t>
+          <t>-7,38; 19,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 18,39</t>
+          <t>-9,61; 18,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 6,89</t>
+          <t>-13,14; 11,57</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-12,18%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>20,83%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>26,69%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-41,66%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-12,18%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>-6,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-19,51%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 102,87</t>
+          <t>-36,91; 70,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 106,45</t>
+          <t>-50,3; 50,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,98; 11,3</t>
+          <t>-32,19; 67,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 60,49</t>
+          <t>-22,35; 103,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,19; 48,67</t>
+          <t>-17,22; 115,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 67,37</t>
+          <t>-43,88; 51,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 58,75</t>
+          <t>-16,06; 57,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 57,87</t>
+          <t>-21,5; 54,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,21; 18,85</t>
+          <t>-27,92; 35,91</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-4,49</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,74</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>8,99</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>5,74</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7,29</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-4,49</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>15,75</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>8,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 17,8</t>
+          <t>-10,88; 6,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 14,37</t>
+          <t>-13,99; 4,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 18,84</t>
+          <t>-6,81; 11,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 8,12</t>
+          <t>-0,53; 17,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 4,43</t>
+          <t>-2,4; 14,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 11,47</t>
+          <t>5,79; 24,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,34</t>
+          <t>-3,55; 8,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 6,99</t>
+          <t>-5,98; 7,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 12,2</t>
+          <t>2,44; 15,27</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-5,36%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-10,89%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>27,29%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>17,41%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-5,36%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-10,89%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 63,21</t>
+          <t>-24,42; 16,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 50,83</t>
+          <t>-31,09; 12,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 63,66</t>
+          <t>-15,78; 31,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 22,71</t>
+          <t>-1,21; 61,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 11,69</t>
+          <t>-6,92; 55,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 32,37</t>
+          <t>16,42; 90,06</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 27,49</t>
+          <t>-8,5; 25,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 20,91</t>
+          <t>-14,85; 20,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 35,18</t>
+          <t>6,13; 46,06</t>
         </is>
       </c>
     </row>
